--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-J171-TypeAutorisation-EPARS.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-J171-TypeAutorisation-EPARS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="77">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240329120000</t>
+    <t>20241118120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T12:00:00+01:00</t>
+    <t>2024-11-18T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -229,6 +229,12 @@
   </si>
   <si>
     <t>Agrément de radiophysicien avant le 28/11/2004</t>
+  </si>
+  <si>
+    <t>AM42</t>
+  </si>
+  <si>
+    <t>Autorisation d'user du titre de Psychothérapeute</t>
   </si>
   <si>
     <t/>
@@ -507,7 +513,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -695,15 +701,23 @@
         <v>72</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>74</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
